--- a/.cursor/scratch/tax_turbo_parts/ASK Mercury.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/ASK Mercury.xlsx
@@ -77,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -85,6 +85,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -453,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -464,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ASK — Mercury 8291 (answer these so EPGC Consultant / remaining sales can be booked). Not tax advice.</t>
+          <t>ASK — remaining Mercury 8291 questions. Q6 David Aaron consultant fee and Q8 Koziol/Ariadne pass-through LOCKED 2026-09-20. Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -542,14 +548,14 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>6. David Aaron Limited $13,595 IN (6/24)</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Proposed art sale (London antiquities dealer invoice). Confirm object. If it is a purchase you paid and they refunded, say so.</t>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>6. David Aaron Limited $13,595 IN (6/24) — LOCKED consultant fee</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>CONFIRMED 2026-09-20: consultant fee, not a sale. Booked EPGC Consultant June $13,595 (peach). Not Art Sales. Not Income I8.</t>
         </is>
       </c>
     </row>
@@ -566,14 +572,14 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>8. Jack Koziol &amp; Tracy Hoffman $150,000 IN (10/20) / Ariadne Demirjian $150,000 OUT (10/21)</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Proposed pass-through (not P&amp;L). If this was a real purchase/sale, name the object.</t>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>8. Jack Koziol &amp; Tracy Hoffman $150,000 IN (10/20) / Ariadne Demirjian $150,000 OUT (10/21) — LOCKED pass-through</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>CONFIRMED 2026-09-20: pass-through, not P&amp;L. Not a sale, not a purchase, not COGS, not Consultant.</t>
         </is>
       </c>
     </row>
@@ -610,86 +616,110 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Coinbase ACH net</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>$-51,000.00  (OUT $-59,000.00 / IN $8,000.00) — Investments tab, not EPGC</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>Newstar Jewelers</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>$23,581.00 jewelry fabrication COGS (10/14 $8,000 + 11/12 $8,000 + 12/24 $7,581)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>Berk sales</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>$14,000 seals (1/10) + $30,000 lots (2/7) = $44,000 Art Sales</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>Mosaics</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>EOEB $105,000 sale (2/21) / Plutus $50,000 of $90,000 Cost</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>BoA 9922 draws</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>$261,172.00 owner transfer — not P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>Wise/EOEB 12/2</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>$565.75 reimbursed — not income, not expense</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>$10 test wires</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Jamal Rifai / EPGC / Plutus tests — not P&amp;L</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>David Aaron Limited</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>$13,595 (6/24) consultant fee → EPGC Consultant June. Not a sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Koziol / Ariadne</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>$150,000 IN 10/20 + $150,000 OUT 10/21 LOCKED pass-through — not P&amp;L</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/ASK Mercury.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/ASK Mercury.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ASK — remaining Mercury 8291 questions. Q6 David Aaron consultant fee and Q8 Koziol/Ariadne pass-through LOCKED 2026-09-20. Not tax advice.</t>
+          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise write-ups, Q8 pass-through LOCKED 2026-09-20. Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -560,14 +560,14 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>7. Wise $334.17 (7/9) and $658.63 (10/30)</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Who / what? Dec $565.75 was reimbursed by EOEB (locked net $0). These two were not.</t>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>7. Wise $334.17 (7/9) and $658.63 (10/30) — LOCKED expertise write-ups</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>CONFIRMED 2026-09-20: business expenses (expertise write-ups). Booked EPGC Consultant Fees July $334.17 + October $658.63 = $992.80. Not COGS. Distinct from Dec Wise $565.75 reimbursed by EOEB (still not P&amp;L).</t>
         </is>
       </c>
     </row>
@@ -720,6 +720,18 @@
       <c r="B24" s="7" t="inlineStr">
         <is>
           <t>$150,000 IN 10/20 + $150,000 OUT 10/21 LOCKED pass-through — not P&amp;L</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Wise expertise write-ups</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>$334.17 (7/9) + $658.63 (10/30) = $992.80 → EPGC Consultant Fees expense. Dec $565.75 still reimbursed / not P&amp;L.</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/ASK Mercury.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/ASK Mercury.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise write-ups, Q8 pass-through LOCKED 2026-09-20. Not tax advice.</t>
+          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise write-ups, Q8 pass-through, Q9 Aquinas books LOCKED 2026-09-20. Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -584,14 +584,14 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>9. Aquinas Hobor $1,000 IN (2/4)</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Sale, leftover, or other? Aquinas bought Saharan bracelets in 2022.</t>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>9. Aquinas Hobor $1,000 IN (2/4) — LOCKED books sold</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>CONFIRMED 2026-09-20: books sold to Aquinas. Booked EPGC Art Sales February $1,000 (peach). Cost / titles TBD — not in Income I8 until Cost. Distinct from 2022 Saharan bracelets.</t>
         </is>
       </c>
     </row>
@@ -732,6 +732,18 @@
       <c r="B25" s="7" t="inlineStr">
         <is>
           <t>$334.17 (7/9) + $658.63 (10/30) = $992.80 → EPGC Consultant Fees expense. Dec $565.75 still reimbursed / not P&amp;L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Aquinas Hobor books</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>$1,000 IN 2/4 LOCKED books sold → EPGC Art Sales February. Cost / titles TBD (not in I8 until Cost).</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/ASK Mercury.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/ASK Mercury.xlsx
@@ -470,7 +470,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise write-ups, Q8 pass-through, Q9 Aquinas books LOCKED 2026-09-20. Not tax advice.</t>
+          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise, Q8 pass-through, Q9 Aquinas books LOCKED (green). Q1/Q2 mixed pattern CONFIRMED, dollars unallocated (yellow). Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -490,24 +490,24 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1. EOEB LLC remainder after mosaics</t>
+          <t>1. EOEB LLC remainder after mosaics — MIXED PATTERN CONFIRMED, dollars unallocated</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>$130,270.00 of EOEB IN is not the $105,000 mosaics sale and not the $565.75 Wise reimbursement. Invoice / MAKE A PAYMENT pattern. Book as art advisory (EPGC Consultant) or as more art sales? Jan 16 $1,000 might be the Canosan horse (sold to Erdal $1,000 on Art Sales) — yes/no?</t>
+          <t>$130,270.00 of EOEB IN is not mosaics $105,000 and not Wise reimburse $565.75. User 2026-09-20: EOEB is mixed art sales AND advisory/consultant fees. Do NOT dump this remainder onto Consultant or Art Sales. Invoice-level split still ASK. Jan 16 $1,000 Canosan-horse question STILL OPEN (Art Sales horse is to Erdal; this cash is EOEB).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>2. L5 (all seven invoices)</t>
+          <t>2. L5 (all seven invoices) — MIXED PATTERN CONFIRMED, dollars unallocated</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>$87,396.32. Same Auto-Routing Request or Invoice Payment pattern as EOEB. Advisory fees, art sales, or mixed? The 7/15 $50,000 lands the same week as Aysel $50k and Fortuna $45k.</t>
+          <t>$87,396.32. User 2026-09-20: L5 is mixed art sales AND advisory/consultant fees. Do NOT dump onto Consultant or Art Sales. Invoice-level split still ASK. The 7/15 $50,000 still sits in the Aysel $50k / Fortuna $45k week.</t>
         </is>
       </c>
     </row>
@@ -586,12 +586,12 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>9. Aquinas Hobor $1,000 IN (2/4) — LOCKED books sold</t>
+          <t>9. Aquinas Hobor $1,000 IN (2/4) — LOCKED book sale</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>CONFIRMED 2026-09-20: books sold to Aquinas. Booked EPGC Art Sales February $1,000 (peach). Cost / titles TBD — not in Income I8 until Cost. Distinct from 2022 Saharan bracelets.</t>
+          <t>CONFIRMED 2026-09-20: book SALE. Hits EPGC Art Sales February +$1,000 (Feb $136,000; matched cash $150,000). Art Sales register: Books (titles TBD) to Aquinas Hobor, Sale Price $1,000, Sale Date 2025-02-04, Cost TBD. Not in Income I8 until Cost (same as Sale 6428).</t>
         </is>
       </c>
     </row>
@@ -743,7 +743,7 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>$1,000 IN 2/4 LOCKED books sold → EPGC Art Sales February. Cost / titles TBD (not in I8 until Cost).</t>
+          <t>$1,000 IN 2/4 LOCKED book sale → EPGC Art Sales February +$1,000 (Feb $136,000; matched cash $150,000). Cost / titles TBD (not in I8 until Cost, same as Sale 6428).</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/ASK Mercury.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/ASK Mercury.xlsx
@@ -41,7 +41,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +51,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -77,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -93,7 +98,13 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -459,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -470,7 +481,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise, Q8 pass-through, Q9 Aquinas books LOCKED (green). Q1/Q2 mixed pattern CONFIRMED, dollars unallocated (yellow). Not tax advice.</t>
+          <t>ASK — remaining Mercury 8291 questions. Q6 consultant, Q7 Wise expertise, Q8 pass-through, Q9 Aquinas books LOCKED (green). Q1/Q2 mixed pattern CONFIRMED (blue) — remainder dollars unallocated until invoice split. Not tax advice.</t>
         </is>
       </c>
     </row>
@@ -495,7 +506,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>$130,270.00 of EOEB IN is not mosaics $105,000 and not Wise reimburse $565.75. User 2026-09-20: EOEB is mixed art sales AND advisory/consultant fees. Do NOT dump this remainder onto Consultant or Art Sales. Invoice-level split still ASK. Jan 16 $1,000 Canosan-horse question STILL OPEN (Art Sales horse is to Erdal; this cash is EOEB).</t>
+          <t>$130,270.00 of EOEB IN is not mosaics $105,000 and not Wise reimburse $565.75. User 2026-09-20: EOEB is mixed art sales AND advisory/consultant fees. Do NOT dump this remainder onto Consultant or Art Sales. Mark each invoice sale vs advisory: 1/16 $1,000 (Canosan-horse STILL OPEN — Art Sales horse is to Erdal, this cash is EOEB); 3/10 $14,000; 5/1 $21,000; 5/13 $16,200; 6/12 $25,000 + $3,300; 7/8 $2,000; 8/29 $10,000; 9/19 $5,000; 9/25 $3,100; 10/1 $10,000; 10/15 $16,000; 10/24 $1,500; 10/31 $2,170.</t>
         </is>
       </c>
     </row>
@@ -507,101 +518,101 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>$87,396.32. User 2026-09-20: L5 is mixed art sales AND advisory/consultant fees. Do NOT dump onto Consultant or Art Sales. Invoice-level split still ASK. The 7/15 $50,000 still sits in the Aysel $50k / Fortuna $45k week.</t>
+          <t>$87,396.32. User 2026-09-20: L5 is mixed art sales AND advisory/consultant fees. Do NOT dump onto Consultant or Art Sales. Mark each invoice sale vs advisory: 7/11 $8,534.79; 7/15 $50,000 + $2,500 (same week as Aysel $50k / Fortuna $45k); 9/2 $5,042; 9/23 $9,119.27; 10/21 $7,500; 12/4 $4,700.26.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>3. Fortuna / Erdal Dere OUT after seals</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>$85,000.00 after the 1/8 $13,000 seals COGS (5/9 $20k, 7/21 $45k, 8/15 $20k). Inventory purchases (object names) or something else?</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>4. Erdal Dere IN</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>$57,000.00 (7/24 $26k, 10/9 $25k, 11/7 $6k ‘FORTUNA PAYMENT’). Sales to Erdal, refunds of Fortuna purchases, or other?</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>5. Aysel Dere $50,000 IN (7/18)</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Sale, related-party transfer, or part of the mid-July Fortuna/L5 cluster?</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>6. David Aaron Limited $13,595 IN (6/24) — LOCKED consultant fee</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: consultant fee, not a sale. Booked EPGC Consultant June $13,595 (peach). Not Art Sales. Not Income I8.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>7. Wise $334.17 (7/9) and $658.63 (10/30) — LOCKED expertise write-ups</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: business expenses (expertise write-ups). Booked EPGC Consultant Fees July $334.17 + October $658.63 = $992.80. Not COGS. Distinct from Dec Wise $565.75 reimbursed by EOEB (still not P&amp;L).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>8. Jack Koziol &amp; Tracy Hoffman $150,000 IN (10/20) / Ariadne Demirjian $150,000 OUT (10/21) — LOCKED pass-through</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: pass-through, not P&amp;L. Not a sale, not a purchase, not COGS, not Consultant.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>9. Aquinas Hobor $1,000 IN (2/4) — LOCKED book sale</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>CONFIRMED 2026-09-20: book SALE. Hits EPGC Art Sales February +$1,000 (Feb $136,000; matched cash $150,000). Art Sales register: Books (titles TBD) to Aquinas Hobor, Sale Price $1,000, Sale Date 2025-02-04, Cost TBD. Not in Income I8 until Cost (same as Sale 6428).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>10. Mosaics Cost $90,000 vs Mercury $50,000</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>Plutus &amp; Mnemosyne paid $50,000 in February. Where is the other $40,000 of Cost (other account / 2024 / still owed)?</t>
         </is>
@@ -616,134 +627,146 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>Coinbase ACH net</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>$-51,000.00  (OUT $-59,000.00 / IN $8,000.00) — Investments tab, not EPGC</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Newstar Jewelers</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>$23,581.00 jewelry fabrication COGS (10/14 $8,000 + 11/12 $8,000 + 12/24 $7,581)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>Berk sales</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>$14,000 seals (1/10) + $30,000 lots (2/7) = $44,000 Art Sales</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Mosaics</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>EOEB $105,000 sale (2/21) / Plutus $50,000 of $90,000 Cost</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>BoA 9922 draws</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>$261,172.00 owner transfer — not P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Wise/EOEB 12/2</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>$565.75 reimbursed — not income, not expense</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>$10 test wires</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Jamal Rifai / EPGC / Plutus tests — not P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>David Aaron Limited</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>$13,595 (6/24) consultant fee → EPGC Consultant June. Not a sale.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>Koziol / Ariadne</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>$150,000 IN 10/20 + $150,000 OUT 10/21 LOCKED pass-through — not P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Wise expertise write-ups</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>$334.17 (7/9) + $658.63 (10/30) = $992.80 → EPGC Consultant Fees expense. Dec $565.75 still reimbursed / not P&amp;L.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>Aquinas Hobor books</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>$1,000 IN 2/4 LOCKED book sale → EPGC Art Sales February +$1,000 (Feb $136,000; matched cash $150,000). Cost / titles TBD (not in I8 until Cost, same as Sale 6428).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>EOEB / L5 mixed pattern</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>CONFIRMED mixed art sales AND advisory/consultant. Remainder $130,270 / $87,396.32 unallocated — not on P&amp;L until invoice split. Jan 16 $1,000 Canosan-horse still open.</t>
         </is>
       </c>
     </row>

--- a/.cursor/scratch/tax_turbo_parts/ASK Mercury.xlsx
+++ b/.cursor/scratch/tax_turbo_parts/ASK Mercury.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -525,12 +525,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>3. Fortuna / Erdal Dere OUT after seals</t>
+          <t>3. Fortuna / Erdal $20,000 Aug — object still unnamed</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>$85,000.00 after the 1/8 $13,000 seals COGS (5/9 $20k, 7/21 $45k, 8/15 $20k). Inventory purchases (object names) or something else?</t>
+          <t>$20,000.00. Monarch posted 8/15 = Mercury native initiated 8/18 (same cash, not a second unique txn). Native memo has no object name. Venus $20,000 (5/9) and Roman Gold Belt $45,000 (7/21) are LOCKED inventory below — not this question.</t>
         </is>
       </c>
     </row>
@@ -549,12 +549,12 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>5. Aysel Dere $50,000 IN (7/18)</t>
+          <t>5. Aysel Dere $50,000 — Monarch IN vs native Failed OUT</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Sale, related-party transfer, or part of the mid-July Fortuna/L5 cluster?</t>
+          <t>Monarch 7/18 +$50,000 IN is in the 64. Mercury native CSV has NO Sent Aysel cash — only Failed $50,000 OUT 7/17 'Recipient account does not exist'. Is the Monarch IN a phantom of the failed send, or a real incoming the export omitted? Do not dump onto Art Sales or Consultant until confirmed.</t>
         </is>
       </c>
     </row>
@@ -767,6 +767,42 @@
       <c r="B27" s="9" t="inlineStr">
         <is>
           <t>CONFIRMED mixed art sales AND advisory/consultant. Remainder $130,270 / $87,396.32 unallocated — not on P&amp;L until invoice split. Jan 16 $1,000 Canosan-horse still open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Fortuna Venus inventory</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>$20,000 OUT 5/9 LOCKED. Mercury native note: bronze head of a goddess, likely Venus. Parked Cost — not sold 2025, not dumped onto Art Sales/Consultant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Fortuna Roman Gold Belt</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>$45,000 OUT 7/21 LOCKED. Mercury native note: Roman Gold Belt. Parked Cost — not sold 2025, not dumped onto Art Sales/Consultant.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Native CSV 2026-09-20</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>epgc-llc-transactions-2025-jan-01-to-2025-dec-31.csv is account 8291, same 2025 year already classified. 0 new unique Sent cash vs the 64. Failed Aysel 7/17 and Cancelled Erdal 1/8 are not cash.</t>
         </is>
       </c>
     </row>
